--- a/public/dosen_universitas_ngudi_waluyo.xlsx
+++ b/public/dosen_universitas_ngudi_waluyo.xlsx
@@ -1779,22 +1779,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ANA PUJI ASTUTI</t>
+          <t>AGITYA RESTI ERWIYANI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6146672</t>
+          <t>6082202</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 12</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1805,44 +1805,44 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>566</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6146672</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6082202</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AGITYA RESTI ERWIYANI</t>
+          <t>ANA PUJI ASTUTI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6082202</t>
+          <t>6146672</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 12</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1853,22 +1853,22 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>471</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>170</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6082202</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6146672</t>
         </is>
       </c>
     </row>
@@ -1923,22 +1923,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PUJI LESTARI</t>
+          <t>IKA NILAWATI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6093197</t>
+          <t>6785923</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Ilmu Keolahragaan (S1)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 10</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1949,44 +1949,44 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>303</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>195</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6093197</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6785923</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IKA NILAWATI</t>
+          <t>HANI IRHAMDESSETYA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6785923</t>
+          <t>6813565</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ilmu Keolahragaan (S1)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1997,44 +1997,44 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>408</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6785923</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6813565</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HANI IRHAMDESSETYA</t>
+          <t>PUJI LESTARI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6813565</t>
+          <t>6093197</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2045,22 +2045,22 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>530</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>130</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6813565</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6093197</t>
         </is>
       </c>
     </row>
@@ -3123,22 +3123,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FIKTINA VIFRI ISMIRIYAM</t>
+          <t>ISFAIZAH</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>6138998</t>
+          <t>6085376</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Kebidanan (S1)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3149,44 +3149,44 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6138998</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6085376</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ISFAIZAH</t>
+          <t>FIKTINA VIFRI ISMIRIYAM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>6085376</t>
+          <t>6138998</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kebidanan (S1)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3197,22 +3197,22 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>391</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>175</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6085376</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6138998</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HERI SUGIARTO</t>
+          <t>RATIH LAILY NURJANAH</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5985236</t>
+          <t>6199137</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Kesehatan Masyarakat (S1)</t>
+          <t>Sastra Inggris (S1)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 2GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -3677,44 +3677,44 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>459</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/5985236</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199137</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>RATIH LAILY NURJANAH</t>
+          <t>HERI SUGIARTO</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>6199137</t>
+          <t>5985236</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sastra Inggris (S1)</t>
+          <t>Kesehatan Masyarakat (S1)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 2GS H-Index : 5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -3725,22 +3725,22 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>372</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199137</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/5985236</t>
         </is>
       </c>
     </row>
@@ -5667,17 +5667,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AR-RAHIIM INNASH</t>
+          <t>ARDA RADITYA TANTRA</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>6895455</t>
+          <t>6832181</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ilmu Hukum (S1)</t>
+          <t>Akuntansi Perpajakan (D4)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5693,39 +5693,39 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>138</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6895455</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6832181</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ARDA RADITYA TANTRA</t>
+          <t>AR-RAHIIM INNASH</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>6832181</t>
+          <t>6895455</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Akuntansi Perpajakan (D4)</t>
+          <t>Ilmu Hukum (S1)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5741,44 +5741,44 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6832181</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6895455</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PUJI AFIATNA</t>
+          <t>GUNTUR RATIH PRESTIFA HERDINATA</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>6198595</t>
+          <t>6828552</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Gizi (S1)</t>
+          <t>Ilmu Keolahragaan (S1)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 2GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -5789,44 +5789,44 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198595</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828552</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>GUNTUR RATIH PRESTIFA HERDINATA</t>
+          <t>PUJI AFIATNA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>6828552</t>
+          <t>6198595</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ilmu Keolahragaan (S1)</t>
+          <t>Gizi (S1)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 2GS H-Index : 7</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -5837,22 +5837,22 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>194</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828552</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198595</t>
         </is>
       </c>
     </row>
@@ -6099,22 +6099,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>KARTIKA SARI</t>
+          <t>MUKHAMAD MUSTAIN</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>6080653</t>
+          <t>6668043</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Pendidikan Profesi Bidan (Profesi)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>181</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -6135,34 +6135,34 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6080653</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6668043</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MUKHAMAD MUSTAIN</t>
+          <t>KARTIKA SARI</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>6668043</t>
+          <t>6080653</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Pendidikan Profesi Bidan (Profesi)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6668043</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6080653</t>
         </is>
       </c>
     </row>
@@ -6723,22 +6723,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SUWANTI</t>
+          <t>SALSABIELA DWIYUDRISA SUYUDI</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>6198864</t>
+          <t>6828726</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 2</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -6749,44 +6749,44 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198864</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828726</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SALSABIELA DWIYUDRISA SUYUDI</t>
+          <t>SUWANTI</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>6828726</t>
+          <t>6198864</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 2</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -6797,22 +6797,22 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>149</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828726</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198864</t>
         </is>
       </c>
     </row>
@@ -8163,17 +8163,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>DWI WISNU KURNIAWAN</t>
+          <t>FIKRI ARIYAD</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>6967441</t>
+          <t>6837372</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Ilmu Hukum (S1)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -8204,29 +8204,29 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6967441</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6837372</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FIKRI ARIYAD</t>
+          <t>MUFTI AGUNG WIBOWO</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>6837372</t>
+          <t>6871253</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bisnis Digital (S1)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 1GS H-Index : 0</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -8237,44 +8237,44 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6837372</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6871253</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>MUFTI AGUNG WIBOWO</t>
+          <t>DWI WISNU KURNIAWAN</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>6871253</t>
+          <t>6967441</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bisnis Digital (S1)</t>
+          <t>Ilmu Hukum (S1)</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 0</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6871253</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6967441</t>
         </is>
       </c>
     </row>

--- a/public/dosen_universitas_ngudi_waluyo.xlsx
+++ b/public/dosen_universitas_ngudi_waluyo.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J167"/>
+  <dimension ref="A1:J148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,12 +792,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>849</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>540</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -963,417 +963,417 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UMI ANIROH</t>
+          <t>DIAN OKTIANTI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6198559</t>
+          <t>6105550</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Profesi Ners (Profesi)</t>
+          <t>Profesi Apoteker (Profesi)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 9</t>
+          <t>Scopus H-Index : 0GS H-Index : 8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>267</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>606</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>95</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198559</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6105550</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ARISTA CANDRA IRAWATI</t>
+          <t>IDA SOFIYANTI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6089491</t>
+          <t>156312</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ilmu Hukum (S1)</t>
+          <t>Pendidikan Profesi Bidan (Profesi)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>850</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6089491</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/156312</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SUGENG MARYANTO</t>
+          <t>IWAN SETIAWAN WIBISONO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5994976</t>
+          <t>6125147</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Gizi (S1)</t>
+          <t>Teknik Informatika (S1)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 2GS H-Index : 11</t>
+          <t>Scopus H-Index : 1GS H-Index : 8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.108</t>
+          <t>542</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/5994976</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6125147</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IRSAL FAUZI</t>
+          <t>KARTIKA YUNI PURWANTI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6811146</t>
+          <t>6198670</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bisnis Digital (S1)</t>
+          <t>Pendidikan Guru Sekolah Dasar (S1)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>844</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>295</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6811146</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198670</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GIPTA GALIH WIDODO</t>
+          <t>ALFAN AFANDI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6138830</t>
+          <t>6198600</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Profesi Ners (Profesi)</t>
+          <t>Kesehatan Masyarakat (S1)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 1GS H-Index : 7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>415</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6138830</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198600</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ELA SURYANI</t>
+          <t>YOANNES ROMANDO SIPAYUNG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6067178</t>
+          <t>6126857</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pendidikan Guru Sekolah Dasar (S1)</t>
+          <t>Teknik Informatika (S1)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 13</t>
+          <t>Scopus H-Index : 1GS H-Index : 7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>436</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6067178</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6126857</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UMMU MUNTAMAH</t>
+          <t>NUR AMIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6134627</t>
+          <t>6762507</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Ilmu Keolahragaan (S1)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 1GS H-Index : 9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>531</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>245</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6134627</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6762507</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SIKNI RETNO KARMININGTYAS</t>
+          <t>AGITYA RESTI ERWIYANI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6090856</t>
+          <t>6082202</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Profesi Apoteker (Profesi)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 12</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>566</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6090856</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6082202</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EKO MARDIYANINGSIH</t>
+          <t>ANA PUJI ASTUTI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6091682</t>
+          <t>6146672</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 9</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>471</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1383,29 +1383,29 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>170</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6091682</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6146672</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SRI MUJIYONO</t>
+          <t>DEWI SIYAMTI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6769124</t>
+          <t>6800634</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Teknik Informatika (S1)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1416,161 +1416,161 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>205</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6769124</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6800634</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DIAN OKTIANTI</t>
+          <t>HANI IRHAMDESSETYA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6105550</t>
+          <t>6813565</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Profesi Apoteker (Profesi)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 8</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>408</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6105550</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6813565</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IDA SOFIYANTI</t>
+          <t>IKA NILAWATI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>156312</t>
+          <t>6785923</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pendidikan Profesi Bidan (Profesi)</t>
+          <t>Ilmu Keolahragaan (S1)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 12</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>303</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>195</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/156312</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6785923</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IWAN SETIAWAN WIBISONO</t>
+          <t>PUJI LESTARI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6125147</t>
+          <t>6093197</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Teknik Informatika (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 8</t>
+          <t>Scopus H-Index : 0GS H-Index : 10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>530</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>130</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1580,232 +1580,232 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6125147</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6093197</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KARTIKA YUNI PURWANTI</t>
+          <t>LIYANOVITASARI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6198670</t>
+          <t>6198609</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pendidikan Guru Sekolah Dasar (S1)</t>
+          <t>Profesi Ners (Profesi)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 10</t>
+          <t>Scopus H-Index : 0GS H-Index : 9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>529</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198670</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198609</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ALFAN AFANDI</t>
+          <t>TEGUH HARSO WIDAGDO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6198600</t>
+          <t>6811497</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kesehatan Masyarakat (S1)</t>
+          <t>Bisnis Manajemen Retail (D4)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198600</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6811497</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>YOANNES ROMANDO SIPAYUNG</t>
+          <t>PRIYANTO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6126857</t>
+          <t>6198556</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Teknik Informatika (S1)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 7</t>
+          <t>Scopus H-Index : 4GS H-Index : 6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>604</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>360</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6126857</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198556</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NUR AMIN</t>
+          <t>SYIFA FAUZIAH</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6762507</t>
+          <t>6198681</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ilmu Keolahragaan (S1)</t>
+          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 9</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>448</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>310</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6762507</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198681</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AGITYA RESTI ERWIYANI</t>
+          <t>WAHYU KRISTININGRUM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6082202</t>
+          <t>6198792</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Kebidanan (S1)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 12</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>459</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1815,456 +1815,456 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6082202</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198792</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ANA PUJI ASTUTI</t>
+          <t>NOOR LAILA RAMADHANI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6146672</t>
+          <t>6786224</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Pendidikan Vokasional Desain Fashion (S1)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>371</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>130</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>230</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6146672</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6786224</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DEWI SIYAMTI</t>
+          <t>RICHA YUSWANTINA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6800634</t>
+          <t>6090847</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 9</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>632</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6800634</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6090847</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IKA NILAWATI</t>
+          <t>SIGIT AMBAR WIDYAWATI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6785923</t>
+          <t>6116540</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ilmu Keolahragaan (S1)</t>
+          <t>Kesehatan Masyarakat (S1)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 1GS H-Index : 8</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>490</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6785923</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6116540</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HANI IRHAMDESSETYA</t>
+          <t>VISTRA VEFTISIA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6813565</t>
+          <t>6083935</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Kebidanan (S1)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>182</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>503</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6813565</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6083935</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PUJI LESTARI</t>
+          <t>UNTARI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6093197</t>
+          <t>6898575</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Gizi (S1)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 10</t>
+          <t>Scopus H-Index : 0GS H-Index : 2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>178</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>145</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6093197</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6898575</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LIYANOVITASARI</t>
+          <t>FITRI DWI JAYANTI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6198609</t>
+          <t>6654655</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Profesi Ners (Profesi)</t>
+          <t>Akuntansi Perpajakan (D4)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 9</t>
+          <t>Scopus H-Index : 0GS H-Index : 10</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>177</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>532</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>195</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198609</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6654655</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TEGUH HARSO WIDAGDO</t>
+          <t>MONECA DIAH LISTIYANINGSIH</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6811497</t>
+          <t>6083939</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bisnis Manajemen Retail (D4)</t>
+          <t>Pendidikan Profesi Bidan (Profesi)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>176</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>349</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6811497</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6083939</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PRIYANTO</t>
+          <t>HAPSARI WINDAYANTI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6198556</t>
+          <t>6120215</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Kebidanan (S1)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 4GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 9</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>176</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>570</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198556</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6120215</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SYIFA FAUZIAH</t>
+          <t>FIKTINA VIFRI ISMIRIYAM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6198681</t>
+          <t>6138998</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>175</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>391</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>175</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198681</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6138998</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>WAHYU KRISTININGRUM</t>
+          <t>ISFAIZAH</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6198792</t>
+          <t>6085376</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2274,66 +2274,66 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>175</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198792</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6085376</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NOOR LAILA RAMADHANI</t>
+          <t>SRI WAHYUNI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6786224</t>
+          <t>6798057</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pendidikan Vokasional Desain Fashion (S1)</t>
+          <t>Kesehatan Masyarakat (S1)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>175</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2343,312 +2343,312 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>255</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6786224</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6798057</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RICHA YUSWANTINA</t>
+          <t>NATALIA DEVI OKTARINA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6090847</t>
+          <t>6150329</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 9</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>173</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>390</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6090847</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6150329</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LUVI DIAN AFRIYANI</t>
+          <t>ANNI MALIHATUL HAWA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6073766</t>
+          <t>6093533</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kebidanan (S1)</t>
+          <t>Pendidikan Guru Sekolah Dasar (S1)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 9</t>
+          <t>Scopus H-Index : 1GS H-Index : 9</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>171</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>402</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>170</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6073766</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6093533</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MONA SAPARWATI</t>
+          <t>ZULMI ROESTIKA RINI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6145016</t>
+          <t>6741160</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Pendidikan Guru Sekolah Dasar (S1)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 11</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>167</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6145016</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6741160</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NIKEN DYAHARIESTI</t>
+          <t>FIKI WIJAYANTI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6124013</t>
+          <t>6140123</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Profesi Apoteker (Profesi)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 10</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>162</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>453</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>155</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6124013</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6140123</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HESTI YUNITIARA RIZQI</t>
+          <t>YULIA NUR KHAYATI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6803409</t>
+          <t>6099236</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pendidikan Guru Sekolah Dasar (S1)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 8</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>159</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>476</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6803409</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6099236</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>INDRI MULYASARI</t>
+          <t>UMI HANDAYANI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6134609</t>
+          <t>6735858</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Gizi (S1)</t>
+          <t>Sastra Jepang (S1)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 11</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>157</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>135</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6134609</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6735858</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EKO NUR HERMANSYAH</t>
+          <t>SETYA INDAH ISNAWATI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6904295</t>
+          <t>6810538</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2658,23 +2658,23 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>154</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>311</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2684,163 +2684,163 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6904295</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6810538</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MELATI APRILLIANA RAMADHANI</t>
+          <t>KARTIKA DIAN PERTIWI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6755940</t>
+          <t>6752546</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Kesehatan Masyarakat (S1)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>152</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6755940</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6752546</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>WULANSARI</t>
+          <t>HERI SUGIARTO</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6150389</t>
+          <t>5985236</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Kesehatan Masyarakat (S1)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 2GS H-Index : 5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>151</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>372</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6150389</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/5985236</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RISMA ALIVIANI PUTRI</t>
+          <t>RATIH LAILY NURJANAH</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>6083924</t>
+          <t>6199137</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kebidanan (S1)</t>
+          <t>Sastra Inggris (S1)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>151</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>459</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6083924</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199137</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SIGIT AMBAR WIDYAWATI</t>
+          <t>SRI LESTARI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6116540</t>
+          <t>6773656</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2850,18 +2850,18 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 8</t>
+          <t>Scopus H-Index : 0GS H-Index : 2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2871,29 +2871,29 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6116540</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6773656</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>VISTRA VEFTISIA</t>
+          <t>ABDUL AZIZ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6083935</t>
+          <t>6811145</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kebidanan (S1)</t>
+          <t>Bisnis Digital (S1)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2904,65 +2904,65 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>148</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>309</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6083935</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6811145</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>UNTARI</t>
+          <t>JOYO MINARDO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>6898575</t>
+          <t>6148988</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Gizi (S1)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 2</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>147</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>349</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2972,136 +2972,136 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6898575</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6148988</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FITRI DWI JAYANTI</t>
+          <t>DEWI ROSNITA HARDIANY</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6654655</t>
+          <t>6198611</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Akuntansi Perpajakan (D4)</t>
+          <t>Sastra Inggris (S1)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 10</t>
+          <t>Scopus H-Index : 0GS H-Index : 2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>147</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6654655</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198611</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MONECA DIAH LISTIYANINGSIH</t>
+          <t>ZUMROTUL CHAIRIJAH</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>6083939</t>
+          <t>6089858</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pendidikan Profesi Bidan (Profesi)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>145</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>145</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>215</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6083939</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6089858</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HAPSARI WINDAYANTI</t>
+          <t>ITA PUJI LESTARI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6120215</t>
+          <t>6198573</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kebidanan (S1)</t>
+          <t>Kesehatan Masyarakat (S1)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 9</t>
+          <t>Scopus H-Index : 0GS H-Index : 8</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>142</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>322</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3111,168 +3111,168 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6120215</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198573</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ISFAIZAH</t>
+          <t>ANASTHASIA PUJIASTUTI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>6085376</t>
+          <t>6104015</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kebidanan (S1)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>141</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6085376</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6104015</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FIKTINA VIFRI ISMIRIYAM</t>
+          <t>SWANTYKA ILHAM PRAHESTI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>6138998</t>
+          <t>6198675</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>141</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>354</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6138998</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198675</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SRI WAHYUNI</t>
+          <t>AHMAD ALI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6798057</t>
+          <t>6784204</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kesehatan Masyarakat (S1)</t>
+          <t>Bisnis Manajemen Retail (D4)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 12</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>133</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6798057</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6784204</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NATALIA DEVI OKTARINA</t>
+          <t>YUNITA GALIH YUDANARI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>6150329</t>
+          <t>6159734</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3282,290 +3282,290 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>131</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>258</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6150329</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6159734</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ANNI MALIHATUL HAWA</t>
+          <t>ETI SALAFAS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6093533</t>
+          <t>6070451</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Pendidikan Guru Sekolah Dasar (S1)</t>
+          <t>Kebidanan (S1)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 9</t>
+          <t>Scopus H-Index : 0GS H-Index : 9</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>131</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>470</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6093533</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6070451</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ZULMI ROESTIKA RINI</t>
+          <t>RINA PURWANTI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>6741160</t>
+          <t>6799993</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pendidikan Guru Sekolah Dasar (S1)</t>
+          <t>Pendidikan Vokasional Desain Fashion (S1)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>130</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>228</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>147</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6741160</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6799993</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FIKI WIJAYANTI</t>
+          <t>ADE PRATAMA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>6140123</t>
+          <t>6864477</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Teknik Informatika (S1)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>129</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>167</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6140123</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6864477</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>YULIA NUR KHAYATI</t>
+          <t>WIDAYATI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6099236</t>
+          <t>6197290</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Kebidanan (S1)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 8</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>129</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>266</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6099236</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6197290</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>UMI HANDAYANI</t>
+          <t>RIVA MUSTIKA ANUGRAH</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>6735858</t>
+          <t>6198592</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sastra Jepang (S1)</t>
+          <t>Gizi (S1)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 1GS H-Index : 7</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>128</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>408</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6735858</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198592</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SETYA INDAH ISNAWATI</t>
+          <t>MASRUROH</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>6810538</t>
+          <t>6137636</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bisnis Digital (S1)</t>
+          <t>Kebidanan (S1)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3576,7 +3576,7 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>128</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3586,322 +3586,322 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6810538</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6137636</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>KARTIKA DIAN PERTIWI</t>
+          <t>DEVI MARDIYANTI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>6752546</t>
+          <t>6827820</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kesehatan Masyarakat (S1)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>127</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>210</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6752546</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6827820</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>RATIH LAILY NURJANAH</t>
+          <t>ENDANG KUSUMA ASTUTI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>6199137</t>
+          <t>6026487</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sastra Inggris (S1)</t>
+          <t>Ilmu Hukum (S1)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 1GS H-Index : 7</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>126</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>584</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>410</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199137</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6026487</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HERI SUGIARTO</t>
+          <t>JAYA RAMADAEY BANGSA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5985236</t>
+          <t>6783116</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kesehatan Masyarakat (S1)</t>
+          <t>Bisnis Digital (S1)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 2GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>122</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>172</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/5985236</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6783116</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SRI LESTARI</t>
+          <t>UMI SETYONINGRUM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>6773656</t>
+          <t>6198571</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Kesehatan Masyarakat (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 2</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6773656</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198571</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ABDUL AZIZ</t>
+          <t>ROSALINA WAHYU RIANI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>6811145</t>
+          <t>6199234</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bisnis Digital (S1)</t>
+          <t>Sastra Jepang (S1)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>118</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>228</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>135</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6811145</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199234</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>JOYO MINARDO</t>
+          <t>BAMBANG AHMAD INDARTO</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>6148988</t>
+          <t>6864285</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Akuntansi Perpajakan (D4)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6148988</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6864285</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DEWI ROSNITA HARDIANY</t>
+          <t>CHINDYA PARAMITHA DEVI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>6198611</t>
+          <t>6904288</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sastra Inggris (S1)</t>
+          <t>Gizi (S1)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3912,231 +3912,231 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198611</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6904288</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ZUMROTUL CHAIRIJAH</t>
+          <t>YULIAJI SISWANTO</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>6089858</t>
+          <t>6092843</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Kesehatan Masyarakat (S1)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 12</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>443</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6089858</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6092843</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ITA PUJI LESTARI</t>
+          <t>ARI WIDYANINGSIH</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>6198573</t>
+          <t>6659244</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Kesehatan Masyarakat (S1)</t>
+          <t>Pendidikan Profesi Bidan (Profesi)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 8</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>276</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198573</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6659244</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ANASTHASIA PUJIASTUTI</t>
+          <t>EKA ADIMAYANTI</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>6104015</t>
+          <t>6135410</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 0GS H-Index : 10</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>470</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>215</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6104015</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6135410</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SWANTYKA ILHAM PRAHESTI</t>
+          <t>MOCHAMAD RIZQI ADHI PRATAMA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>6198675</t>
+          <t>6199090</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
+          <t>Sastra Inggris (S1)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 1GS H-Index : 5</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>241</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198675</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199090</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AHMAD ALI</t>
+          <t>SUDIYONO</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>6784204</t>
+          <t>6811477</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4146,333 +4146,333 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 12</t>
+          <t>Scopus H-Index : 0GS H-Index : 10</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>169</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6784204</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6811477</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>YUNITA GALIH YUDANARI</t>
+          <t>ARI ANDAYANI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>6159734</t>
+          <t>6083837</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Pendidikan Profesi Bidan (Profesi)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>264</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6159734</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6083837</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ETI SALAFAS</t>
+          <t>ARI SISWATI</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>6070451</t>
+          <t>6828399</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kebidanan (S1)</t>
+          <t>Bisnis Digital (S1)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 9</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>108</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>146</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6070451</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828399</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>RINA PURWANTI</t>
+          <t>PUJI PURWANINGSIH</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>6799993</t>
+          <t>6022997</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Pendidikan Vokasional Desain Fashion (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>107</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>320</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6799993</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6022997</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ADE PRATAMA</t>
+          <t>HENDRIKE PRIVENTA</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>6864477</t>
+          <t>6832244</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Teknik Informatika (S1)</t>
+          <t>Sastra Jepang (S1)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 2</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>106</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>239</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6864477</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6832244</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>WIDAYATI</t>
+          <t>BUDIATI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>6197290</t>
+          <t>6090401</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Kebidanan (S1)</t>
+          <t>Sastra Inggris (S1)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>289</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>185</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6197290</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6090401</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>RIVA MUSTIKA ANUGRAH</t>
+          <t>ISRI NASIFAH</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>6198592</t>
+          <t>6139595</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Gizi (S1)</t>
+          <t>Pendidikan Profesi Bidan (Profesi)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 7</t>
+          <t>Scopus H-Index : 1GS H-Index : 3</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>228</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198592</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6139595</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MASRUROH</t>
+          <t>NINIK CHRISTIANI</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>6137636</t>
+          <t>6087332</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4482,45 +4482,45 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>259</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6137636</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6087332</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DEVI MARDIYANTI</t>
+          <t>DEDI HASWAN</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>6827820</t>
+          <t>6788031</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4530,258 +4530,258 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 2</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>163</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6827820</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6788031</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ENDANG KUSUMA ASTUTI</t>
+          <t>FARIDAH AINI</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>6026487</t>
+          <t>6105503</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ilmu Hukum (S1)</t>
+          <t>Profesi Ners (Profesi)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 10</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>362</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>145</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6026487</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6105503</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>JAYA RAMADAEY BANGSA</t>
+          <t>HARGIANTI DINI ISWANDARI</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>6783116</t>
+          <t>6645959</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bisnis Digital (S1)</t>
+          <t>Ilmu Hukum (S1)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 1GS H-Index : 2</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>99</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>287</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6783116</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6645959</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>UMI SETYONINGRUM</t>
+          <t>NELI DIAH PRATIWI</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>6198571</t>
+          <t>6829033</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198571</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6829033</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ROSALINA WAHYU RIANI</t>
+          <t>GALEH SEPTIAR PONTANG</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>6199234</t>
+          <t>6142769</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sastra Jepang (S1)</t>
+          <t>Gizi (S1)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 1GS H-Index : 7</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>97</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>473</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199234</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6142769</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BAMBANG AHMAD INDARTO</t>
+          <t>AR-RAHIIM INNASH</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>6864285</t>
+          <t>6895455</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Akuntansi Perpajakan (D4)</t>
+          <t>Ilmu Hukum (S1)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>96</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4791,333 +4791,333 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6864285</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6895455</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CHINDYA PARAMITHA DEVI</t>
+          <t>ARDA RADITYA TANTRA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>6904288</t>
+          <t>6832181</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Gizi (S1)</t>
+          <t>Akuntansi Perpajakan (D4)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 2</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>96</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>138</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6904288</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6832181</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>YULIAJI SISWANTO</t>
+          <t>PUJI AFIATNA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>6092843</t>
+          <t>6198595</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kesehatan Masyarakat (S1)</t>
+          <t>Gizi (S1)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 12</t>
+          <t>Scopus H-Index : 2GS H-Index : 7</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>194</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6092843</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198595</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ARI WIDYANINGSIH</t>
+          <t>GUNTUR RATIH PRESTIFA HERDINATA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>6659244</t>
+          <t>6828552</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Pendidikan Profesi Bidan (Profesi)</t>
+          <t>Ilmu Keolahragaan (S1)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6659244</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828552</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EKA ADIMAYANTI</t>
+          <t>ANITA KUMALA HATI</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>6135410</t>
+          <t>6198526</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Profesi Apoteker (Profesi)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 10</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>93</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>248</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6135410</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198526</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MOCHAMAD RIZQI ADHI PRATAMA</t>
+          <t>ROSALINA</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>6199090</t>
+          <t>6130613</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sastra Inggris (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>91</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199090</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6130613</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SUDIYONO</t>
+          <t>SETIAJI WISNU WARDANA</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>6811477</t>
+          <t>6910728</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bisnis Manajemen Retail (D4)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 10</t>
+          <t>Scopus H-Index : 0GS H-Index : 1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>87</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>87</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6811477</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910728</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ARI ANDAYANI</t>
+          <t>ARISTIYANTO</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>6083837</t>
+          <t>6661976</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Pendidikan Profesi Bidan (Profesi)</t>
+          <t>Ilmu Keolahragaan (S1)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>86</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5127,242 +5127,242 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6083837</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6661976</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ARI SISWATI</t>
+          <t>HENI SETYOWATI</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>6828399</t>
+          <t>6092183</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bisnis Digital (S1)</t>
+          <t>Kebidanan (S1)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 10</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>381</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828399</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6092183</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PUJI PURWANINGSIH</t>
+          <t>KARTIKA SARI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>6022997</t>
+          <t>6080653</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Pendidikan Profesi Bidan (Profesi)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6022997</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6080653</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>HENDRIKE PRIVENTA</t>
+          <t>MUKHAMAD MUSTAIN</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>6832244</t>
+          <t>6668043</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sastra Jepang (S1)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>181</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6832244</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6668043</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BUDIATI</t>
+          <t>JATMIKO SUSILO</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>6090401</t>
+          <t>6125921</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sastra Inggris (S1)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 8</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>79</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>404</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6090401</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6125921</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ISRI NASIFAH</t>
+          <t>ARIYANTI</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>6139595</t>
+          <t>6962874</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Pendidikan Profesi Bidan (Profesi)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5372,307 +5372,307 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6139595</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6962874</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>NINIK CHRISTIANI</t>
+          <t>ENDANG SUSILOWATI</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>6087332</t>
+          <t>6142883</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Kebidanan (S1)</t>
+          <t>Sastra Inggris (S1)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6087332</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6142883</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DEDI HASWAN</t>
+          <t>NUFITRIANI KARTIKA DEWI</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>6788031</t>
+          <t>6198683</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 2</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6788031</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198683</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FARIDAH AINI</t>
+          <t>TRIMAWATI</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>6105503</t>
+          <t>6138716</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Profesi Ners (Profesi)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 10</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>73</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6105503</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6138716</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>HARGIANTI DINI ISWANDARI</t>
+          <t>HENI HIRAWATI PRANOTO</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>6645959</t>
+          <t>6095701</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ilmu Hukum (S1)</t>
+          <t>Pendidikan Profesi Bidan (Profesi)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 2</t>
+          <t>Scopus H-Index : 1GS H-Index : 7</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>72</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>191</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6645959</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6095701</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>NELI DIAH PRATIWI</t>
+          <t>NUR INTAN ROCHMAWATI</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>6829033</t>
+          <t>6165083</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 1GS H-Index : 6</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6829033</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6165083</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GALEH SEPTIAR PONTANG</t>
+          <t>ARI EKO BUDIYANTO</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>6142769</t>
+          <t>6784934</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Gizi (S1)</t>
+          <t>Pendidikan Vokasional Desain Fashion (S1)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>69</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>156</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6142769</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6784934</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ARDA RADITYA TANTRA</t>
+          <t>BULAN KARIMA NURANI</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>6832181</t>
+          <t>6876121</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5682,50 +5682,50 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 1</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>65</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6832181</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6876121</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AR-RAHIIM INNASH</t>
+          <t>EKO SUSILO</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>6895455</t>
+          <t>6198745</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ilmu Hukum (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5736,60 +5736,60 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>65</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>282</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>125</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6895455</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198745</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>GUNTUR RATIH PRESTIFA HERDINATA</t>
+          <t>MUHAMAD LATIF</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>6828552</t>
+          <t>6906186</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ilmu Keolahragaan (S1)</t>
+          <t>Ilmu Hukum (S1)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>63</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5799,381 +5799,381 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828552</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6906186</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PUJI AFIATNA</t>
+          <t>SUWANTI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>6198595</t>
+          <t>6198864</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Gizi (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 2GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>61</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>149</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198595</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198864</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ANITA KUMALA HATI</t>
+          <t>SALSABIELA DWIYUDRISA SUYUDI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>6198526</t>
+          <t>6828726</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Profesi Apoteker (Profesi)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 2</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>61</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198526</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828726</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ROSALINA</t>
+          <t>RINI SUSANTI</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>6130613</t>
+          <t>6198686</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Kebidanan (S1)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 2</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>61</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6130613</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198686</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SETIAJI WISNU WARDANA</t>
+          <t>HIMMAH TAULANY</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>6910728</t>
+          <t>6198769</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 1</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910728</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198769</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ARISTIYANTO</t>
+          <t>AL HAJAR FUADATUS ZURROH</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>6661976</t>
+          <t>6880920</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ilmu Keolahragaan (S1)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 1</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>58</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6661976</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6880920</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>HENI SETYOWATI</t>
+          <t>ABDUL WAKHID</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>6092183</t>
+          <t>6091883</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Kebidanan (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 10</t>
+          <t>Scopus H-Index : 2GS H-Index : 13</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>414</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6092183</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6091883</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MUKHAMAD MUSTAIN</t>
+          <t>CAHYANINGRUM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>6668043</t>
+          <t>6137288</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Kebidanan (S1)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6668043</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6137288</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>KARTIKA SARI</t>
+          <t>WIWIK PUDJANINGSIH</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>6080653</t>
+          <t>6654803</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Pendidikan Profesi Bidan (Profesi)</t>
+          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6188,40 +6188,40 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6080653</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6654803</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>JATMIKO SUSILO</t>
+          <t>MAKSUM</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>6125921</t>
+          <t>6798396</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 8</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>66</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6231,317 +6231,317 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6125921</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6798396</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ARIYANTI</t>
+          <t>DESWANDITO DWI SAPTANTO</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>6962874</t>
+          <t>6199470</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Sastra Inggris (S1)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6962874</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199470</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ENDANG SUSILOWATI</t>
+          <t>PURWOSIWI PANDANSARI</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>6142883</t>
+          <t>6799938</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Sastra Inggris (S1)</t>
+          <t>Pendidikan Vokasional Desain Fashion (S1)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6142883</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6799938</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>NUFITRIANI KARTIKA DEWI</t>
+          <t>TEGUH SANTOSO</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>6198683</t>
+          <t>6199112</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
+          <t>Sastra Jepang (S1)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>38</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>175</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198683</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199112</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TRIMAWATI</t>
+          <t>ABDUL RONI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>6138716</t>
+          <t>6769758</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6138716</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6769758</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>HENI HIRAWATI PRANOTO</t>
+          <t>TRI SUSILO</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>6095701</t>
+          <t>6801098</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Pendidikan Profesi Bidan (Profesi)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>95</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6095701</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6801098</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>NUR INTAN ROCHMAWATI</t>
+          <t>MUHAMMAD IMRON ROSYIDI</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>6165083</t>
+          <t>6022748</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
+          <t>Profesi Ners (Profesi)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6165083</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6022748</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ARI EKO BUDIYANTO</t>
+          <t>INDRA YULIAWAN</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>6784934</t>
+          <t>6140645</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Pendidikan Vokasional Desain Fashion (S1)</t>
+          <t>Ilmu Hukum (S1)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6552,39 +6552,39 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>135</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6784934</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6140645</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BULAN KARIMA NURANI</t>
+          <t>DEWI ARI ANI</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>6876121</t>
+          <t>6817968</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -6600,12 +6600,12 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6620,184 +6620,184 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6876121</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6817968</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EKO SUSILO</t>
+          <t>AHMAD KHOLID</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>6198745</t>
+          <t>6737399</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>191</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198745</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6737399</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MUHAMAD LATIF</t>
+          <t>MAYA KURNIA DEWI</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>6906186</t>
+          <t>6138989</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ilmu Hukum (S1)</t>
+          <t>Sastra Inggris (S1)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6906186</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6138989</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SALSABIELA DWIYUDRISA SUYUDI</t>
+          <t>FREDY EKO SETIAWAN</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>6828726</t>
+          <t>6828557</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Ilmu Keolahragaan (S1)</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 2</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828726</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828557</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SUWANTI</t>
+          <t>KRISTANTI</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>6198864</t>
+          <t>6897130</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Pendidikan Vokasional Desain Fashion (S1)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 2</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6807,47 +6807,47 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198864</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6897130</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RINI SUSANTI</t>
+          <t>RAHARJO APRIYATMOKO</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>6198686</t>
+          <t>6198558</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Kebidanan (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 2</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="H134" t="inlineStr">
         <is>
           <t>0</t>
@@ -6855,120 +6855,120 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198686</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198558</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>HIMMAH TAULANY</t>
+          <t>NASRI</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>6198769</t>
+          <t>6198568</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
+          <t>Ilmu Keolahragaan (S1)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>143</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198769</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198568</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AL HAJAR FUADATUS ZURROH</t>
+          <t>YENI INDRANINGTYAS</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>6880920</t>
+          <t>6993258</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Bisnis Manajemen Retail (D4)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 1</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6880920</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6993258</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ABDUL WAKHID</t>
+          <t>SUKARNO</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>6091883</t>
+          <t>6198543</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -6978,18 +6978,18 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 2GS H-Index : 13</t>
+          <t>Scopus H-Index : 0GS H-Index : 14</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>356</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6999,93 +6999,93 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6091883</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198543</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CAHYANINGRUM</t>
+          <t>TUSI WIRAHAYU PERTIWI</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>6137288</t>
+          <t>6967446</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Kebidanan (S1)</t>
+          <t>Ilmu Hukum (S1)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6137288</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6967446</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>WIWIK PUDJANINGSIH</t>
+          <t>FITRIA PRIMI ASTUTI</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>6654803</t>
+          <t>6082432</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>174</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -7100,40 +7100,40 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6654803</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6082432</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MAKSUM</t>
+          <t>ANDI PRADANA</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>6798396</t>
+          <t>6910783</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 1</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -7148,136 +7148,136 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6798396</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910783</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>DESWANDITO DWI SAPTANTO</t>
+          <t>INDAH KURNIAWATI</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>6199470</t>
+          <t>6910777</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Sastra Inggris (S1)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199470</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910777</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PURWOSIWI PANDANSARI</t>
+          <t>ANDI PRADANA</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>6799938</t>
+          <t>6910783</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Pendidikan Vokasional Desain Fashion (S1)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 1</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6799938</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910783</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TEGUH SANTOSO</t>
+          <t>FIKRI ARIYAD</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>6199112</t>
+          <t>6837372</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Sastra Jepang (S1)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -7287,45 +7287,45 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199112</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6837372</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ABDUL RONI</t>
+          <t>MUFTI AGUNG WIBOWO</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>6769758</t>
+          <t>6871253</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Bisnis Digital (S1)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 1GS H-Index : 0</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -7335,120 +7335,120 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6769758</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6871253</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>TRI SUSILO</t>
+          <t>DWI RETNA SUSILOWATI</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>6801098</t>
+          <t>6895451</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6801098</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6895451</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MUHAMMAD IMRON ROSYIDI</t>
+          <t>ADI PURWANTO</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>6022748</t>
+          <t>6198866</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Profesi Ners (Profesi)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6022748</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198866</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>INDRA YULIAWAN</t>
+          <t>DWI WISNU KURNIAWAN</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>6140645</t>
+          <t>6967441</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -7458,18 +7458,18 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -7479,45 +7479,45 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6140645</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6967441</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DEWI ARI ANI</t>
+          <t>ARI PARDI</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>6817968</t>
+          <t>6996658</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Akuntansi Perpajakan (D4)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 1</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -7531,918 +7531,6 @@
         </is>
       </c>
       <c r="J148" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6817968</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>AHMAD KHOLID</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>6737399</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Keperawatan (D3)</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6737399</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>MAYA KURNIA DEWI</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>6138989</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Sastra Inggris (S1)</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6138989</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>FREDY EKO SETIAWAN</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>6828557</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Ilmu Keolahragaan (S1)</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828557</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>KRISTANTI</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>6897130</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Pendidikan Vokasional Desain Fashion (S1)</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Scopus H-Index : 0GS H-Index : 2</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6897130</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>RAHARJO APRIYATMOKO</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>6198558</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Keperawatan (S1)</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198558</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>NASRI</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>6198568</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Ilmu Keolahragaan (S1)</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198568</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>YENI INDRANINGTYAS</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>6993258</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Bisnis Manajemen Retail (D4)</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6993258</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>TUSI WIRAHAYU PERTIWI</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>6967446</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Ilmu Hukum (S1)</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6967446</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>SUKARNO</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>6198543</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Keperawatan (S1)</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Scopus H-Index : 0GS H-Index : 14</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>356</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198543</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>SITI KHOIRIYAH</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>6910724</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Farmasi (S1)</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910724</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>FITRIA PRIMI ASTUTI</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>6082432</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6082432</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>ANDI PRADANA</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>6910783</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Farmasi (S1)</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Scopus H-Index : 0GS H-Index : 1</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910783</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>INDAH KURNIAWATI</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>6910777</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Farmasi (S1)</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910777</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>FIKRI ARIYAD</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>6837372</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6837372</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>MUFTI AGUNG WIBOWO</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>6871253</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Bisnis Digital (S1)</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Scopus H-Index : 1GS H-Index : 0</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6871253</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>DWI WISNU KURNIAWAN</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>6967441</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Ilmu Hukum (S1)</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6967441</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>DWI RETNA SUSILOWATI</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>6895451</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Farmasi (S1)</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6895451</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>ADI PURWANTO</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>6198866</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198866</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>ARI PARDI</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>6996658</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
         <is>
           <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6996658</t>
         </is>

--- a/public/dosen_universitas_ngudi_waluyo.xlsx
+++ b/public/dosen_universitas_ngudi_waluyo.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J148"/>
+  <dimension ref="A1:J168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -963,417 +963,417 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DIAN OKTIANTI</t>
+          <t>UMI ANIROH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6105550</t>
+          <t>6198559</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Profesi Apoteker (Profesi)</t>
+          <t>Profesi Ners (Profesi)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 8</t>
+          <t>Scopus H-Index : 0GS H-Index : 9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>332</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>796</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>230</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>460</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6105550</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198559</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IDA SOFIYANTI</t>
+          <t>ARISTA CANDRA IRAWATI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>156312</t>
+          <t>6089491</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pendidikan Profesi Bidan (Profesi)</t>
+          <t>Ilmu Hukum (S1)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 12</t>
+          <t>Scopus H-Index : 1GS H-Index : 6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>318</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>715</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/156312</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6089491</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IWAN SETIAWAN WIBISONO</t>
+          <t>SUGENG MARYANTO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6125147</t>
+          <t>5994976</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Teknik Informatika (S1)</t>
+          <t>Gizi (S1)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 8</t>
+          <t>Scopus H-Index : 2GS H-Index : 11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>314</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>1.108</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6125147</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/5994976</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KARTIKA YUNI PURWANTI</t>
+          <t>IRSAL FAUZI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6198670</t>
+          <t>6811146</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pendidikan Guru Sekolah Dasar (S1)</t>
+          <t>Bisnis Digital (S1)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 10</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>313</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>439</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198670</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6811146</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ALFAN AFANDI</t>
+          <t>GIPTA GALIH WIDODO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6198600</t>
+          <t>6138830</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kesehatan Masyarakat (S1)</t>
+          <t>Profesi Ners (Profesi)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>304</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>578</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>205</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>320</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198600</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6138830</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>YOANNES ROMANDO SIPAYUNG</t>
+          <t>ELA SURYANI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6126857</t>
+          <t>6067178</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Teknik Informatika (S1)</t>
+          <t>Pendidikan Guru Sekolah Dasar (S1)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 7</t>
+          <t>Scopus H-Index : 1GS H-Index : 13</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>302</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>380</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6126857</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6067178</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NUR AMIN</t>
+          <t>UMMU MUNTAMAH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6762507</t>
+          <t>6134627</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ilmu Keolahragaan (S1)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 9</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>296</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>734</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6762507</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6134627</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AGITYA RESTI ERWIYANI</t>
+          <t>SIKNI RETNO KARMININGTYAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6082202</t>
+          <t>6090856</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Profesi Apoteker (Profesi)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 12</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>286</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>465</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>205</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6082202</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6090856</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ANA PUJI ASTUTI</t>
+          <t>EKO MARDIYANINGSIH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6146672</t>
+          <t>6091682</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 1GS H-Index : 9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>576</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1383,29 +1383,29 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>260</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6146672</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6091682</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DEWI SIYAMTI</t>
+          <t>SRI MUJIYONO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6800634</t>
+          <t>6769124</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Teknik Informatika (S1)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1416,161 +1416,161 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>268</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>584</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>255</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6800634</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6769124</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HANI IRHAMDESSETYA</t>
+          <t>DIAN OKTIANTI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6813565</t>
+          <t>6105550</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Profesi Apoteker (Profesi)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>267</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>606</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>95</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6813565</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6105550</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IKA NILAWATI</t>
+          <t>IDA SOFIYANTI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6785923</t>
+          <t>156312</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ilmu Keolahragaan (S1)</t>
+          <t>Pendidikan Profesi Bidan (Profesi)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>850</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6785923</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/156312</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PUJI LESTARI</t>
+          <t>IWAN SETIAWAN WIBISONO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6093197</t>
+          <t>6125147</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Teknik Informatika (S1)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 10</t>
+          <t>Scopus H-Index : 1GS H-Index : 8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>542</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1580,691 +1580,691 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6093197</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6125147</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LIYANOVITASARI</t>
+          <t>KARTIKA YUNI PURWANTI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6198609</t>
+          <t>6198670</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Profesi Ners (Profesi)</t>
+          <t>Pendidikan Guru Sekolah Dasar (S1)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 9</t>
+          <t>Scopus H-Index : 0GS H-Index : 10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>844</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>295</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198609</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198670</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TEGUH HARSO WIDAGDO</t>
+          <t>ALFAN AFANDI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6811497</t>
+          <t>6198600</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bisnis Manajemen Retail (D4)</t>
+          <t>Kesehatan Masyarakat (S1)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 1GS H-Index : 7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>415</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6811497</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198600</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PRIYANTO</t>
+          <t>YOANNES ROMANDO SIPAYUNG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6198556</t>
+          <t>6126857</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Teknik Informatika (S1)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 4GS H-Index : 6</t>
+          <t>Scopus H-Index : 1GS H-Index : 7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>436</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198556</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6126857</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SYIFA FAUZIAH</t>
+          <t>NUR AMIN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6198681</t>
+          <t>6762507</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
+          <t>Ilmu Keolahragaan (S1)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 1GS H-Index : 9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>531</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>245</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198681</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6762507</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WAHYU KRISTININGRUM</t>
+          <t>ANA PUJI ASTUTI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6198792</t>
+          <t>6146672</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kebidanan (S1)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>471</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>170</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198792</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6146672</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NOOR LAILA RAMADHANI</t>
+          <t>AGITYA RESTI ERWIYANI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6786224</t>
+          <t>6082202</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pendidikan Vokasional Desain Fashion (S1)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 12</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>566</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6786224</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6082202</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RICHA YUSWANTINA</t>
+          <t>DEWI SIYAMTI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6090847</t>
+          <t>6800634</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 9</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>205</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6090847</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6800634</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SIGIT AMBAR WIDYAWATI</t>
+          <t>HANI IRHAMDESSETYA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6116540</t>
+          <t>6813565</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kesehatan Masyarakat (S1)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 8</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>408</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6116540</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6813565</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>VISTRA VEFTISIA</t>
+          <t>PUJI LESTARI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6083935</t>
+          <t>6093197</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kebidanan (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 10</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>530</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>130</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6083935</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6093197</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>UNTARI</t>
+          <t>IKA NILAWATI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6898575</t>
+          <t>6785923</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gizi (S1)</t>
+          <t>Ilmu Keolahragaan (S1)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 2</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>303</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>195</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6898575</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6785923</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FITRI DWI JAYANTI</t>
+          <t>LIYANOVITASARI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6654655</t>
+          <t>6198609</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Akuntansi Perpajakan (D4)</t>
+          <t>Profesi Ners (Profesi)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 10</t>
+          <t>Scopus H-Index : 0GS H-Index : 9</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>529</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6654655</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198609</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MONECA DIAH LISTIYANINGSIH</t>
+          <t>TEGUH HARSO WIDAGDO</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6083939</t>
+          <t>6811497</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pendidikan Profesi Bidan (Profesi)</t>
+          <t>Bisnis Manajemen Retail (D4)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6083939</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6811497</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HAPSARI WINDAYANTI</t>
+          <t>PRIYANTO</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6120215</t>
+          <t>6198556</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kebidanan (S1)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 9</t>
+          <t>Scopus H-Index : 4GS H-Index : 6</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>604</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>360</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6120215</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198556</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FIKTINA VIFRI ISMIRIYAM</t>
+          <t>SYIFA FAUZIAH</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6138998</t>
+          <t>6198681</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>448</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>310</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6138998</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198681</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ISFAIZAH</t>
+          <t>WAHYU KRISTININGRUM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6085376</t>
+          <t>6198792</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2274,66 +2274,66 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>459</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6085376</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198792</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SRI WAHYUNI</t>
+          <t>NOOR LAILA RAMADHANI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6798057</t>
+          <t>6786224</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kesehatan Masyarakat (S1)</t>
+          <t>Pendidikan Vokasional Desain Fashion (S1)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>371</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2343,312 +2343,312 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>230</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6798057</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6786224</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NATALIA DEVI OKTARINA</t>
+          <t>RICHA YUSWANTINA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6150329</t>
+          <t>6090847</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 9</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>632</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6150329</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6090847</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ANNI MALIHATUL HAWA</t>
+          <t>LUVI DIAN AFRIYANI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6093533</t>
+          <t>6073766</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pendidikan Guru Sekolah Dasar (S1)</t>
+          <t>Kebidanan (S1)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 9</t>
+          <t>Scopus H-Index : 0GS H-Index : 9</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>212</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>484</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6093533</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6073766</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ZULMI ROESTIKA RINI</t>
+          <t>MONA SAPARWATI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6741160</t>
+          <t>6145016</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pendidikan Guru Sekolah Dasar (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 11</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>211</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>593</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6741160</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6145016</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FIKI WIJAYANTI</t>
+          <t>NIKEN DYAHARIESTI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6140123</t>
+          <t>6124013</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Profesi Apoteker (Profesi)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 10</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>210</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>450</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6140123</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6124013</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>YULIA NUR KHAYATI</t>
+          <t>HESTI YUNITIARA RIZQI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6099236</t>
+          <t>6803409</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Pendidikan Guru Sekolah Dasar (S1)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 8</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>206</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>246</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6099236</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6803409</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>UMI HANDAYANI</t>
+          <t>INDRI MULYASARI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6735858</t>
+          <t>6134609</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sastra Jepang (S1)</t>
+          <t>Gizi (S1)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 1GS H-Index : 11</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>205</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>857</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6735858</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6134609</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SETYA INDAH ISNAWATI</t>
+          <t>EKO NUR HERMANSYAH</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6810538</t>
+          <t>6904295</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2658,23 +2658,23 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>202</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>275</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>115</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2684,312 +2684,312 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6810538</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6904295</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KARTIKA DIAN PERTIWI</t>
+          <t>MELATI APRILLIANA RAMADHANI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6752546</t>
+          <t>6755940</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kesehatan Masyarakat (S1)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>201</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>376</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6752546</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6755940</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>HERI SUGIARTO</t>
+          <t>WULANSARI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5985236</t>
+          <t>6150389</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kesehatan Masyarakat (S1)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 2GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>196</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>414</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>175</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/5985236</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6150389</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RATIH LAILY NURJANAH</t>
+          <t>RISMA ALIVIANI PUTRI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>6199137</t>
+          <t>6083924</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sastra Inggris (S1)</t>
+          <t>Kebidanan (S1)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>518</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>95</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199137</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6083924</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SRI LESTARI</t>
+          <t>SITI MUTMAINAH</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6773656</t>
+          <t>6927670</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kesehatan Masyarakat (S1)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 2</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>192</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>264</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6773656</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6927670</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ABDUL AZIZ</t>
+          <t>SIGIT AMBAR WIDYAWATI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6811145</t>
+          <t>6116540</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bisnis Digital (S1)</t>
+          <t>Kesehatan Masyarakat (S1)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 1GS H-Index : 8</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>490</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6811145</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6116540</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JOYO MINARDO</t>
+          <t>VISTRA VEFTISIA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>6148988</t>
+          <t>6083935</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Kebidanan (S1)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>182</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>503</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6148988</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6083935</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DEWI ROSNITA HARDIANY</t>
+          <t>UNTARI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6198611</t>
+          <t>6898575</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sastra Inggris (S1)</t>
+          <t>Gizi (S1)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3000,188 +3000,188 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>178</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>145</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198611</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6898575</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ZUMROTUL CHAIRIJAH</t>
+          <t>FITRI DWI JAYANTI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>6089858</t>
+          <t>6654655</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Akuntansi Perpajakan (D4)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 10</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>177</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>532</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>195</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6089858</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6654655</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ITA PUJI LESTARI</t>
+          <t>MONECA DIAH LISTIYANINGSIH</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6198573</t>
+          <t>6083939</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kesehatan Masyarakat (S1)</t>
+          <t>Pendidikan Profesi Bidan (Profesi)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 8</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>176</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>349</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198573</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6083939</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ANASTHASIA PUJIASTUTI</t>
+          <t>HAPSARI WINDAYANTI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>6104015</t>
+          <t>6120215</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Kebidanan (S1)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 0GS H-Index : 9</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>176</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>570</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6104015</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6120215</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SWANTYKA ILHAM PRAHESTI</t>
+          <t>ISFAIZAH</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>6198675</t>
+          <t>6085376</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
+          <t>Kebidanan (S1)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3192,92 +3192,92 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>175</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198675</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6085376</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AHMAD ALI</t>
+          <t>FIKTINA VIFRI ISMIRIYAM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6784204</t>
+          <t>6138998</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bisnis Manajemen Retail (D4)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 12</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>175</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>391</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>175</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6784204</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6138998</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>YUNITA GALIH YUDANARI</t>
+          <t>SRI WAHYUNI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>6159734</t>
+          <t>6798057</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Kesehatan Masyarakat (S1)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3288,188 +3288,188 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>175</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>130</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>255</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6159734</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6798057</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ETI SALAFAS</t>
+          <t>NATALIA DEVI OKTARINA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6070451</t>
+          <t>6150329</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kebidanan (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 9</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>173</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>390</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6070451</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6150329</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>RINA PURWANTI</t>
+          <t>ANNI MALIHATUL HAWA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>6799993</t>
+          <t>6093533</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pendidikan Vokasional Desain Fashion (S1)</t>
+          <t>Pendidikan Guru Sekolah Dasar (S1)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 1GS H-Index : 9</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>171</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>402</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>170</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6799993</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6093533</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ADE PRATAMA</t>
+          <t>ZULMI ROESTIKA RINI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>6864477</t>
+          <t>6741160</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Teknik Informatika (S1)</t>
+          <t>Pendidikan Guru Sekolah Dasar (S1)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 2</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>167</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6864477</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6741160</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>WIDAYATI</t>
+          <t>FIKI WIJAYANTI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6197290</t>
+          <t>6140123</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kebidanan (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3480,860 +3480,860 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>162</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>453</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>155</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6197290</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6140123</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>RIVA MUSTIKA ANUGRAH</t>
+          <t>YULIA NUR KHAYATI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>6198592</t>
+          <t>6099236</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Gizi (S1)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 8</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>159</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>476</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198592</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6099236</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MASRUROH</t>
+          <t>UMI HANDAYANI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>6137636</t>
+          <t>6735858</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kebidanan (S1)</t>
+          <t>Sastra Jepang (S1)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>157</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>135</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6137636</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6735858</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DEVI MARDIYANTI</t>
+          <t>SETYA INDAH ISNAWATI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>6827820</t>
+          <t>6810538</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Bisnis Digital (S1)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>154</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>311</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>125</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6827820</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6810538</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ENDANG KUSUMA ASTUTI</t>
+          <t>KARTIKA DIAN PERTIWI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>6026487</t>
+          <t>6752546</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ilmu Hukum (S1)</t>
+          <t>Kesehatan Masyarakat (S1)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>152</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6026487</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6752546</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>JAYA RAMADAEY BANGSA</t>
+          <t>HERI SUGIARTO</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>6783116</t>
+          <t>5985236</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bisnis Digital (S1)</t>
+          <t>Kesehatan Masyarakat (S1)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 2GS H-Index : 5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>151</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>372</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6783116</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/5985236</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>UMI SETYONINGRUM</t>
+          <t>RATIH LAILY NURJANAH</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>6198571</t>
+          <t>6199137</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Sastra Inggris (S1)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>151</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>459</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198571</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199137</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ROSALINA WAHYU RIANI</t>
+          <t>SRI LESTARI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>6199234</t>
+          <t>6773656</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sastra Jepang (S1)</t>
+          <t>Kesehatan Masyarakat (S1)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 2</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199234</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6773656</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BAMBANG AHMAD INDARTO</t>
+          <t>ABDUL AZIZ</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>6864285</t>
+          <t>6811145</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Akuntansi Perpajakan (D4)</t>
+          <t>Bisnis Digital (S1)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>148</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>309</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6864285</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6811145</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CHINDYA PARAMITHA DEVI</t>
+          <t>JOYO MINARDO</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>6904288</t>
+          <t>6148988</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Gizi (S1)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 2</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>147</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>349</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>145</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6904288</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6148988</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>YULIAJI SISWANTO</t>
+          <t>DEWI ROSNITA HARDIANY</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>6092843</t>
+          <t>6198611</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Kesehatan Masyarakat (S1)</t>
+          <t>Sastra Inggris (S1)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 12</t>
+          <t>Scopus H-Index : 0GS H-Index : 2</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>147</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6092843</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198611</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ARI WIDYANINGSIH</t>
+          <t>ZUMROTUL CHAIRIJAH</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>6659244</t>
+          <t>6089858</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pendidikan Profesi Bidan (Profesi)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>145</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>145</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>215</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6659244</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6089858</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EKA ADIMAYANTI</t>
+          <t>ITA PUJI LESTARI</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>6135410</t>
+          <t>6198573</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Kesehatan Masyarakat (S1)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 10</t>
+          <t>Scopus H-Index : 0GS H-Index : 8</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>142</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>322</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6135410</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198573</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MOCHAMAD RIZQI ADHI PRATAMA</t>
+          <t>ANASTHASIA PUJIASTUTI</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>6199090</t>
+          <t>6104015</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sastra Inggris (S1)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>141</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199090</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6104015</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SUDIYONO</t>
+          <t>SWANTYKA ILHAM PRAHESTI</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>6811477</t>
+          <t>6198675</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bisnis Manajemen Retail (D4)</t>
+          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 10</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>141</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>354</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6811477</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198675</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ARI ANDAYANI</t>
+          <t>AHMAD ALI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>6083837</t>
+          <t>6784204</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pendidikan Profesi Bidan (Profesi)</t>
+          <t>Bisnis Manajemen Retail (D4)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 12</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>133</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6083837</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6784204</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ARI SISWATI</t>
+          <t>YUNITA GALIH YUDANARI</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>6828399</t>
+          <t>6159734</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bisnis Digital (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>131</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>258</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828399</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6159734</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PUJI PURWANINGSIH</t>
+          <t>ETI SALAFAS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>6022997</t>
+          <t>6070451</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Kebidanan (S1)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 9</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>131</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>470</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6022997</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6070451</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HENDRIKE PRIVENTA</t>
+          <t>RINA PURWANTI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>6832244</t>
+          <t>6799993</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sastra Jepang (S1)</t>
+          <t>Pendidikan Vokasional Desain Fashion (S1)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4344,279 +4344,279 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>130</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>228</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>147</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6832244</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6799993</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BUDIATI</t>
+          <t>ADE PRATAMA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>6090401</t>
+          <t>6864477</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sastra Inggris (S1)</t>
+          <t>Teknik Informatika (S1)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 2</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>129</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>167</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6090401</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6864477</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ISRI NASIFAH</t>
+          <t>WIDAYATI</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>6139595</t>
+          <t>6197290</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Pendidikan Profesi Bidan (Profesi)</t>
+          <t>Kebidanan (S1)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>129</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>266</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6139595</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6197290</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>NINIK CHRISTIANI</t>
+          <t>RIVA MUSTIKA ANUGRAH</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>6087332</t>
+          <t>6198592</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kebidanan (S1)</t>
+          <t>Gizi (S1)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 1GS H-Index : 7</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>128</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>408</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6087332</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198592</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DEDI HASWAN</t>
+          <t>MASRUROH</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>6788031</t>
+          <t>6137636</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Kebidanan (S1)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 2</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>128</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>311</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6788031</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6137636</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FARIDAH AINI</t>
+          <t>DEVI MARDIYANTI</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>6105503</t>
+          <t>6827820</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Profesi Ners (Profesi)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 10</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>127</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>210</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6105503</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6827820</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>HARGIANTI DINI ISWANDARI</t>
+          <t>ENDANG KUSUMA ASTUTI</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>6645959</t>
+          <t>6026487</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4626,146 +4626,146 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 2</t>
+          <t>Scopus H-Index : 1GS H-Index : 7</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>126</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>584</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>410</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6645959</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6026487</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>NELI DIAH PRATIWI</t>
+          <t>JAYA RAMADAEY BANGSA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>6829033</t>
+          <t>6783116</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Bisnis Digital (S1)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>122</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>172</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6829033</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6783116</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GALEH SEPTIAR PONTANG</t>
+          <t>UMI SETYONINGRUM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>6142769</t>
+          <t>6198571</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Gizi (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6142769</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198571</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AR-RAHIIM INNASH</t>
+          <t>ROSALINA WAHYU RIANI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>6895455</t>
+          <t>6199234</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ilmu Hukum (S1)</t>
+          <t>Sastra Jepang (S1)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4776,39 +4776,39 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>118</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>228</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>135</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6895455</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199234</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ARDA RADITYA TANTRA</t>
+          <t>BAMBANG AHMAD INDARTO</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>6832181</t>
+          <t>6864285</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4818,45 +4818,45 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6832181</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6864285</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PUJI AFIATNA</t>
+          <t>CHINDYA PARAMITHA DEVI</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>6198595</t>
+          <t>6904288</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4866,114 +4866,114 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 2GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 2</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198595</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6904288</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>GUNTUR RATIH PRESTIFA HERDINATA</t>
+          <t>YULIAJI SISWANTO</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>6828552</t>
+          <t>6092843</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ilmu Keolahragaan (S1)</t>
+          <t>Kesehatan Masyarakat (S1)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 12</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>443</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828552</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6092843</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ANITA KUMALA HATI</t>
+          <t>ARI WIDYANINGSIH</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>6198526</t>
+          <t>6659244</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Profesi Apoteker (Profesi)</t>
+          <t>Pendidikan Profesi Bidan (Profesi)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>276</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4983,221 +4983,221 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198526</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6659244</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ROSALINA</t>
+          <t>EKA ADIMAYANTI</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>6130613</t>
+          <t>6135410</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 10</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>470</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>215</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6130613</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6135410</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SETIAJI WISNU WARDANA</t>
+          <t>MOCHAMAD RIZQI ADHI PRATAMA</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>6910728</t>
+          <t>6199090</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Sastra Inggris (S1)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 1</t>
+          <t>Scopus H-Index : 1GS H-Index : 5</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>241</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910728</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199090</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ARISTIYANTO</t>
+          <t>SUDIYONO</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>6661976</t>
+          <t>6811477</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ilmu Keolahragaan (S1)</t>
+          <t>Bisnis Manajemen Retail (D4)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 10</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>169</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6661976</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6811477</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>HENI SETYOWATI</t>
+          <t>ARI ANDAYANI</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>6092183</t>
+          <t>6083837</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kebidanan (S1)</t>
+          <t>Pendidikan Profesi Bidan (Profesi)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 10</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>264</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6092183</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6083837</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>KARTIKA SARI</t>
+          <t>ARI SISWATI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>6080653</t>
+          <t>6828399</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Pendidikan Profesi Bidan (Profesi)</t>
+          <t>Bisnis Digital (S1)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5208,12 +5208,12 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>108</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>146</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5228,24 +5228,24 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6080653</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828399</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MUKHAMAD MUSTAIN</t>
+          <t>PUJI PURWANINGSIH</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>6668043</t>
+          <t>6022997</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5256,188 +5256,188 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>107</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>320</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6668043</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6022997</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>JATMIKO SUSILO</t>
+          <t>HENDRIKE PRIVENTA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>6125921</t>
+          <t>6832244</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Sastra Jepang (S1)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 8</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>106</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>239</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6125921</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6832244</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ARIYANTI</t>
+          <t>BUDIATI</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>6962874</t>
+          <t>6090401</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Sastra Inggris (S1)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>289</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>185</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6962874</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6090401</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ENDANG SUSILOWATI</t>
+          <t>ISRI NASIFAH</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>6142883</t>
+          <t>6139595</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sastra Inggris (S1)</t>
+          <t>Pendidikan Profesi Bidan (Profesi)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 1GS H-Index : 3</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>228</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6142883</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6139595</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>NUFITRIANI KARTIKA DEWI</t>
+          <t>NINIK CHRISTIANI</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>6198683</t>
+          <t>6087332</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
+          <t>Kebidanan (S1)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5448,284 +5448,284 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>259</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198683</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6087332</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TRIMAWATI</t>
+          <t>DEDI HASWAN</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>6138716</t>
+          <t>6788031</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 2</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>163</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6138716</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6788031</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>HENI HIRAWATI PRANOTO</t>
+          <t>FARIDAH AINI</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>6095701</t>
+          <t>6105503</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Pendidikan Profesi Bidan (Profesi)</t>
+          <t>Profesi Ners (Profesi)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 10</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>362</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>145</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6095701</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6105503</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>NUR INTAN ROCHMAWATI</t>
+          <t>HARGIANTI DINI ISWANDARI</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>6165083</t>
+          <t>6645959</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
+          <t>Ilmu Hukum (S1)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 6</t>
+          <t>Scopus H-Index : 1GS H-Index : 2</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>99</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>287</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6165083</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6645959</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ARI EKO BUDIYANTO</t>
+          <t>NELI DIAH PRATIWI</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>6784934</t>
+          <t>6829033</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Pendidikan Vokasional Desain Fashion (S1)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>97</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6784934</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6829033</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BULAN KARIMA NURANI</t>
+          <t>GALEH SEPTIAR PONTANG</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>6876121</t>
+          <t>6142769</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Akuntansi Perpajakan (D4)</t>
+          <t>Gizi (S1)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 1</t>
+          <t>Scopus H-Index : 1GS H-Index : 7</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>97</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>473</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6876121</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6142769</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EKO SUSILO</t>
+          <t>ARDA RADITYA TANTRA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>6198745</t>
+          <t>6832181</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Akuntansi Perpajakan (D4)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5736,204 +5736,204 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>96</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>138</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198745</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6832181</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MUHAMAD LATIF</t>
+          <t>ARDA RADITYA TANTRA</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>6906186</t>
+          <t>6832181</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ilmu Hukum (S1)</t>
+          <t>Akuntansi Perpajakan (D4)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>96</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>138</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6906186</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6832181</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SUWANTI</t>
+          <t>PUJI AFIATNA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>6198864</t>
+          <t>6198595</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Gizi (S1)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 2GS H-Index : 7</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>194</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198864</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198595</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SALSABIELA DWIYUDRISA SUYUDI</t>
+          <t>GUNTUR RATIH PRESTIFA HERDINATA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>6828726</t>
+          <t>6828552</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Ilmu Keolahragaan (S1)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 2</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828726</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828552</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>RINI SUSANTI</t>
+          <t>ANITA KUMALA HATI</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>6198686</t>
+          <t>6198526</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Kebidanan (S1)</t>
+          <t>Profesi Apoteker (Profesi)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 2</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>93</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>248</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5943,29 +5943,29 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198686</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198526</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>HIMMAH TAULANY</t>
+          <t>ROSALINA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>6198769</t>
+          <t>6130613</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5976,44 +5976,44 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>91</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198769</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6130613</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AL HAJAR FUADATUS ZURROH</t>
+          <t>SETIAJI WISNU WARDANA</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>6880920</t>
+          <t>6910728</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6024,87 +6024,87 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>87</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>87</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6880920</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910728</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ABDUL WAKHID</t>
+          <t>ARISTIYANTO</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>6091883</t>
+          <t>6661976</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Ilmu Keolahragaan (S1)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 2GS H-Index : 13</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>86</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6091883</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6661976</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CAHYANINGRUM</t>
+          <t>HENI SETYOWATI</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>6137288</t>
+          <t>6092183</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6114,66 +6114,66 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 10</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>381</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6137288</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6092183</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>WIWIK PUDJANINGSIH</t>
+          <t>MUKHAMAD MUSTAIN</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>6654803</t>
+          <t>6668043</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>181</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6183,45 +6183,45 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6654803</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6668043</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MAKSUM</t>
+          <t>KARTIKA SARI</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>6798396</t>
+          <t>6080653</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Pendidikan Profesi Bidan (Profesi)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6236,424 +6236,424 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6798396</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6080653</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DESWANDITO DWI SAPTANTO</t>
+          <t>JATMIKO SUSILO</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>6199470</t>
+          <t>6125921</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sastra Inggris (S1)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 8</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>79</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>404</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199470</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6125921</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PURWOSIWI PANDANSARI</t>
+          <t>ARIYANTI</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>6799938</t>
+          <t>6962874</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Pendidikan Vokasional Desain Fashion (S1)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6799938</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6962874</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>TEGUH SANTOSO</t>
+          <t>ENDANG SUSILOWATI</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>6199112</t>
+          <t>6142883</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sastra Jepang (S1)</t>
+          <t>Sastra Inggris (S1)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199112</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6142883</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ABDUL RONI</t>
+          <t>NUFITRIANI KARTIKA DEWI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>6769758</t>
+          <t>6198683</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6769758</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198683</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>TRI SUSILO</t>
+          <t>TRIMAWATI</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>6801098</t>
+          <t>6138716</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>73</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6801098</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6138716</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MUHAMMAD IMRON ROSYIDI</t>
+          <t>HENI HIRAWATI PRANOTO</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>6022748</t>
+          <t>6095701</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Profesi Ners (Profesi)</t>
+          <t>Pendidikan Profesi Bidan (Profesi)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 1GS H-Index : 7</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>72</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>191</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6022748</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6095701</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>INDRA YULIAWAN</t>
+          <t>NUR INTAN ROCHMAWATI</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>6140645</t>
+          <t>6165083</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ilmu Hukum (S1)</t>
+          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 1GS H-Index : 6</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6140645</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6165083</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>DEWI ARI ANI</t>
+          <t>ARI EKO BUDIYANTO</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>6817968</t>
+          <t>6784934</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Akuntansi Perpajakan (D4)</t>
+          <t>Pendidikan Vokasional Desain Fashion (S1)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 1</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>69</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>156</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6817968</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6784934</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AHMAD KHOLID</t>
+          <t>BULAN KARIMA NURANI</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>6737399</t>
+          <t>6876121</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Akuntansi Perpajakan (D4)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 1</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>65</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6668,83 +6668,83 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6737399</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6876121</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MAYA KURNIA DEWI</t>
+          <t>EKO SUSILO</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>6138989</t>
+          <t>6198745</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Sastra Inggris (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>65</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>282</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>125</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6138989</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198745</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FREDY EKO SETIAWAN</t>
+          <t>MUHAMAD LATIF</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>6828557</t>
+          <t>6906186</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ilmu Keolahragaan (S1)</t>
+          <t>Ilmu Hukum (S1)</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>63</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6764,24 +6764,24 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828557</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6906186</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>KRISTANTI</t>
+          <t>SALSABIELA DWIYUDRISA SUYUDI</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>6897130</t>
+          <t>6828726</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Pendidikan Vokasional Desain Fashion (S1)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6792,39 +6792,39 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>61</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6897130</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828726</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RAHARJO APRIYATMOKO</t>
+          <t>SUWANTI</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>6198558</t>
+          <t>6198864</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -6834,18 +6834,18 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>61</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>149</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6855,45 +6855,45 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198558</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198864</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>NASRI</t>
+          <t>RINI SUSANTI</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>6198568</t>
+          <t>6198686</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ilmu Keolahragaan (S1)</t>
+          <t>Kebidanan (S1)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 2</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>61</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6903,141 +6903,141 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198568</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198686</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>YENI INDRANINGTYAS</t>
+          <t>HIMMAH TAULANY</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>6993258</t>
+          <t>6198769</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bisnis Manajemen Retail (D4)</t>
+          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6993258</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198769</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SUKARNO</t>
+          <t>AL HAJAR FUADATUS ZURROH</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>6198543</t>
+          <t>6880920</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 14</t>
+          <t>Scopus H-Index : 0GS H-Index : 1</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>58</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198543</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6880920</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>TUSI WIRAHAYU PERTIWI</t>
+          <t>ABDUL WAKHID</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>6967446</t>
+          <t>6091883</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ilmu Hukum (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 2GS H-Index : 13</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>414</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -7047,93 +7047,93 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6967446</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6091883</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FITRIA PRIMI ASTUTI</t>
+          <t>CAHYANINGRUM</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>6082432</t>
+          <t>6137288</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Kebidanan (S1)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6082432</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6137288</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ANDI PRADANA</t>
+          <t>WIWIK PUDJANINGSIH</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>6910783</t>
+          <t>6654803</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Pendidikan Guru Pendidikan Anak Usia Dini (S1)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 1</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -7148,40 +7148,40 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910783</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6654803</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>INDAH KURNIAWATI</t>
+          <t>MAKSUM</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>6910777</t>
+          <t>6798396</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>66</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -7196,163 +7196,163 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910777</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6798396</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ANDI PRADANA</t>
+          <t>DESWANDITO DWI SAPTANTO</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>6910783</t>
+          <t>6199470</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Sastra Inggris (S1)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 1</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910783</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199470</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FIKRI ARIYAD</t>
+          <t>PURWOSIWI PANDANSARI</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>6837372</t>
+          <t>6799938</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Pendidikan Vokasional Desain Fashion (S1)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6837372</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6799938</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MUFTI AGUNG WIBOWO</t>
+          <t>TEGUH SANTOSO</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>6871253</t>
+          <t>6199112</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bisnis Digital (S1)</t>
+          <t>Sastra Jepang (S1)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 0</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6871253</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199112</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>DWI RETNA SUSILOWATI</t>
+          <t>ABDUL RONI</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>6895451</t>
+          <t>6769758</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -7362,175 +7362,1135 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6895451</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6769758</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ADI PURWANTO</t>
+          <t>TRI SUSILO</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>6198866</t>
+          <t>6801098</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198866</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6801098</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>DWI WISNU KURNIAWAN</t>
+          <t>MUHAMMAD IMRON ROSYIDI</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>6967441</t>
+          <t>6022748</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Ilmu Hukum (S1)</t>
+          <t>Profesi Ners (Profesi)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6967441</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6022748</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ARI PARDI</t>
+          <t>INDRA YULIAWAN</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>6996658</t>
+          <t>6140645</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Ilmu Hukum (S1)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6140645</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>DEWI ARI ANI</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>6817968</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Akuntansi Perpajakan (D4)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Scopus H-Index : 0GS H-Index : 1</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
+      <c r="I149" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6817968</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>AHMAD KHOLID</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>6737399</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Keperawatan (D3)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J148" t="inlineStr">
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6737399</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>MAYA KURNIA DEWI</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>6138989</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Sastra Inggris (S1)</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6138989</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>FREDY EKO SETIAWAN</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>6828557</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Ilmu Keolahragaan (S1)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828557</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>KRISTANTI</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>6897130</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Pendidikan Vokasional Desain Fashion (S1)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Scopus H-Index : 0GS H-Index : 2</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6897130</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>RAHARJO APRIYATMOKO</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>6198558</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Keperawatan (S1)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198558</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>NASRI</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>6198568</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Ilmu Keolahragaan (S1)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198568</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>YENI INDRANINGTYAS</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>6993258</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Bisnis Manajemen Retail (D4)</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6993258</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>SUKARNO</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>6198543</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Keperawatan (S1)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Scopus H-Index : 0GS H-Index : 14</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198543</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>TUSI WIRAHAYU PERTIWI</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>6967446</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Ilmu Hukum (S1)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6967446</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>INDAH KURNIAWATI</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>6910777</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Farmasi (S1)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910777</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>SITI KHOIRIYAH</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>6910724</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Farmasi (S1)</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910724</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>FITRIA PRIMI ASTUTI</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>6082432</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6082432</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>SITI KHOIRIYAH</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>6910724</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Farmasi (S1)</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910724</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>DWI WISNU KURNIAWAN</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>6967441</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Ilmu Hukum (S1)</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6967441</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>FIKRI ARIYAD</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>6837372</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6837372</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>MUFTI AGUNG WIBOWO</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>6871253</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Bisnis Digital (S1)</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Scopus H-Index : 1GS H-Index : 0</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6871253</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>DWI RETNA SUSILOWATI</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>6895451</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Farmasi (S1)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6895451</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>ADI PURWANTO</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>6198866</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198866</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>ARI PARDI</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>6996658</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
         <is>
           <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6996658</t>
         </is>

--- a/public/dosen_universitas_ngudi_waluyo.xlsx
+++ b/public/dosen_universitas_ngudi_waluyo.xlsx
@@ -1779,22 +1779,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ANA PUJI ASTUTI</t>
+          <t>AGITYA RESTI ERWIYANI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6146672</t>
+          <t>6082202</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 12</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1805,44 +1805,44 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>566</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6146672</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6082202</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AGITYA RESTI ERWIYANI</t>
+          <t>ANA PUJI ASTUTI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6082202</t>
+          <t>6146672</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 12</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1853,22 +1853,22 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>471</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>170</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6082202</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6146672</t>
         </is>
       </c>
     </row>
@@ -1971,22 +1971,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PUJI LESTARI</t>
+          <t>IKA NILAWATI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6093197</t>
+          <t>6785923</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Ilmu Keolahragaan (S1)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 10</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1997,44 +1997,44 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>303</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>195</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6093197</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6785923</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IKA NILAWATI</t>
+          <t>PUJI LESTARI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6785923</t>
+          <t>6093197</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ilmu Keolahragaan (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2045,22 +2045,22 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>530</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>130</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6785923</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6093197</t>
         </is>
       </c>
     </row>
@@ -3171,22 +3171,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ISFAIZAH</t>
+          <t>FIKTINA VIFRI ISMIRIYAM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>6085376</t>
+          <t>6138998</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kebidanan (S1)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3197,44 +3197,44 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>391</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>175</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6085376</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6138998</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FIKTINA VIFRI ISMIRIYAM</t>
+          <t>ISFAIZAH</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6138998</t>
+          <t>6085376</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Kebidanan (S1)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -3245,22 +3245,22 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6138998</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6085376</t>
         </is>
       </c>
     </row>
@@ -3699,22 +3699,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HERI SUGIARTO</t>
+          <t>RATIH LAILY NURJANAH</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5985236</t>
+          <t>6199137</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kesehatan Masyarakat (S1)</t>
+          <t>Sastra Inggris (S1)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 2GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -3725,44 +3725,44 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>459</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/5985236</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199137</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>RATIH LAILY NURJANAH</t>
+          <t>HERI SUGIARTO</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>6199137</t>
+          <t>5985236</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sastra Inggris (S1)</t>
+          <t>Kesehatan Masyarakat (S1)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 2GS H-Index : 5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -3773,22 +3773,22 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>372</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199137</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/5985236</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ARDA RADITYA TANTRA</t>
+          <t>AR-RAHIIM INNASH</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>6832181</t>
+          <t>6895455</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Akuntansi Perpajakan (D4)</t>
+          <t>Ilmu Hukum (S1)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5789,44 +5789,44 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6832181</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6895455</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PUJI AFIATNA</t>
+          <t>GUNTUR RATIH PRESTIFA HERDINATA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>6198595</t>
+          <t>6828552</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Gizi (S1)</t>
+          <t>Ilmu Keolahragaan (S1)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 2GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -5837,44 +5837,44 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198595</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828552</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>GUNTUR RATIH PRESTIFA HERDINATA</t>
+          <t>PUJI AFIATNA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>6828552</t>
+          <t>6198595</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ilmu Keolahragaan (S1)</t>
+          <t>Gizi (S1)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 2GS H-Index : 7</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -5885,22 +5885,22 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>194</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828552</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198595</t>
         </is>
       </c>
     </row>
@@ -6147,22 +6147,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MUKHAMAD MUSTAIN</t>
+          <t>KARTIKA SARI</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>6668043</t>
+          <t>6080653</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Keperawatan (D3)</t>
+          <t>Pendidikan Profesi Bidan (Profesi)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 4</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6183,34 +6183,34 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6668043</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6080653</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>KARTIKA SARI</t>
+          <t>MUKHAMAD MUSTAIN</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>6080653</t>
+          <t>6668043</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Pendidikan Profesi Bidan (Profesi)</t>
+          <t>Keperawatan (D3)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 4</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>181</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6231,12 +6231,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6080653</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6668043</t>
         </is>
       </c>
     </row>
@@ -6771,22 +6771,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SALSABIELA DWIYUDRISA SUYUDI</t>
+          <t>SUWANTI</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>6828726</t>
+          <t>6198864</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 2</t>
+          <t>Scopus H-Index : 0GS H-Index : 6</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -6797,44 +6797,44 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>149</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828726</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198864</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SUWANTI</t>
+          <t>SALSABIELA DWIYUDRISA SUYUDI</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>6198864</t>
+          <t>6828726</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 6</t>
+          <t>Scopus H-Index : 0GS H-Index : 2</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -6845,22 +6845,22 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198864</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828726</t>
         </is>
       </c>
     </row>
@@ -7923,22 +7923,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SUKARNO</t>
+          <t>TUSI WIRAHAYU PERTIWI</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>6198543</t>
+          <t>6967446</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Ilmu Hukum (S1)</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 14</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7964,29 +7964,29 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198543</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6967446</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TUSI WIRAHAYU PERTIWI</t>
+          <t>SUKARNO</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>6967446</t>
+          <t>6198543</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ilmu Hukum (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 0GS H-Index : 14</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>356</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -8012,19 +8012,19 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6967446</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198543</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>INDAH KURNIAWATI</t>
+          <t>SITI KHOIRIYAH</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>6910777</t>
+          <t>6910724</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -8060,29 +8060,29 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910777</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910724</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SITI KHOIRIYAH</t>
+          <t>FITRIA PRIMI ASTUTI</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>6910724</t>
+          <t>6082432</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -8093,7 +8093,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>174</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -8108,29 +8108,29 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910724</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6082432</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FITRIA PRIMI ASTUTI</t>
+          <t>ANDI PRADANA</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>6082432</t>
+          <t>6910783</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 1</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -8141,7 +8141,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6082432</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910783</t>
         </is>
       </c>
     </row>

--- a/public/dosen_universitas_ngudi_waluyo.xlsx
+++ b/public/dosen_universitas_ngudi_waluyo.xlsx
@@ -3699,22 +3699,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HERI SUGIARTO</t>
+          <t>RATIH LAILY NURJANAH</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5985236</t>
+          <t>6199137</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kesehatan Masyarakat (S1)</t>
+          <t>Sastra Inggris (S1)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 2GS H-Index : 5</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -3725,44 +3725,44 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>459</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/5985236</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199137</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>RATIH LAILY NURJANAH</t>
+          <t>HERI SUGIARTO</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>6199137</t>
+          <t>5985236</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sastra Inggris (S1)</t>
+          <t>Kesehatan Masyarakat (S1)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 2GS H-Index : 5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -3773,22 +3773,22 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>372</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6199137</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/5985236</t>
         </is>
       </c>
     </row>
@@ -5715,17 +5715,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ARDA RADITYA TANTRA</t>
+          <t>AR-RAHIIM INNASH</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>6832181</t>
+          <t>6895455</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Akuntansi Perpajakan (D4)</t>
+          <t>Ilmu Hukum (S1)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5741,39 +5741,39 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6832181</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6895455</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ARDA RADITYA TANTRA</t>
+          <t>AR-RAHIIM INNASH</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>6832181</t>
+          <t>6895455</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Akuntansi Perpajakan (D4)</t>
+          <t>Ilmu Hukum (S1)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5789,44 +5789,44 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6832181</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6895455</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PUJI AFIATNA</t>
+          <t>GUNTUR RATIH PRESTIFA HERDINATA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>6198595</t>
+          <t>6828552</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Gizi (S1)</t>
+          <t>Ilmu Keolahragaan (S1)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 2GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 3</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -5837,44 +5837,44 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198595</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828552</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>GUNTUR RATIH PRESTIFA HERDINATA</t>
+          <t>PUJI AFIATNA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>6828552</t>
+          <t>6198595</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ilmu Keolahragaan (S1)</t>
+          <t>Gizi (S1)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 3</t>
+          <t>Scopus H-Index : 2GS H-Index : 7</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -5885,22 +5885,22 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>194</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6828552</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198595</t>
         </is>
       </c>
     </row>
@@ -7923,22 +7923,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SUKARNO</t>
+          <t>TUSI WIRAHAYU PERTIWI</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>6198543</t>
+          <t>6967446</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Keperawatan (S1)</t>
+          <t>Ilmu Hukum (S1)</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 14</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7964,29 +7964,29 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198543</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6967446</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TUSI WIRAHAYU PERTIWI</t>
+          <t>SUKARNO</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>6967446</t>
+          <t>6198543</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ilmu Hukum (S1)</t>
+          <t>Keperawatan (S1)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 0GS H-Index : 14</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>356</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -8012,19 +8012,19 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6967446</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198543</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>INDAH KURNIAWATI</t>
+          <t>SITI KHOIRIYAH</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>6910777</t>
+          <t>6910724</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -8060,29 +8060,29 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910777</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910724</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SITI KHOIRIYAH</t>
+          <t>FITRIA PRIMI ASTUTI</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>6910724</t>
+          <t>6082432</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 0GS H-Index : 7</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -8093,7 +8093,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>174</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -8108,29 +8108,29 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910724</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6082432</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FITRIA PRIMI ASTUTI</t>
+          <t>ANDI PRADANA</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>6082432</t>
+          <t>6910783</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 7</t>
+          <t>Scopus H-Index : 0GS H-Index : 1</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -8141,7 +8141,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -8156,19 +8156,19 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6082432</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910783</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SITI KHOIRIYAH</t>
+          <t>ANDI PRADANA</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>6910724</t>
+          <t>6910783</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 0GS H-Index : 1</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -8189,7 +8189,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -8204,24 +8204,24 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910724</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6910783</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>DWI WISNU KURNIAWAN</t>
+          <t>FIKRI ARIYAD</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>6967441</t>
+          <t>6837372</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Ilmu Hukum (S1)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -8252,29 +8252,29 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6967441</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6837372</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FIKRI ARIYAD</t>
+          <t>MUFTI AGUNG WIBOWO</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>6837372</t>
+          <t>6871253</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bisnis Digital (S1)</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 0GS H-Index : 0</t>
+          <t>Scopus H-Index : 1GS H-Index : 0</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -8285,44 +8285,44 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6837372</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6871253</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>MUFTI AGUNG WIBOWO</t>
+          <t>DWI RETNA SUSILOWATI</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>6871253</t>
+          <t>6895451</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bisnis Digital (S1)</t>
+          <t>Farmasi (S1)</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Scopus H-Index : 1GS H-Index : 0</t>
+          <t>Scopus H-Index : 0GS H-Index : 0</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -8343,29 +8343,29 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6871253</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6895451</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>DWI RETNA SUSILOWATI</t>
+          <t>ADI PURWANTO</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>6895451</t>
+          <t>6198866</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Farmasi (S1)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8381,39 +8381,39 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
+      <c r="I166" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6895451</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198866</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ADI PURWANTO</t>
+          <t>DWI WISNU KURNIAWAN</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>6198866</t>
+          <t>6967441</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Ilmu Hukum (S1)</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6198866</t>
+          <t>https://sinta.kemdiktisaintek.go.id/authors/profile/6967441</t>
         </is>
       </c>
     </row>
